--- a/신고신저가_20260820.xlsx
+++ b/신고신저가_20260820.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 머크와 모더나가 공동개발한 흑색종 mRNA 암백신의 3상 성공이 미국 헬스케어 전체를 끌어올려, 새로 신고가에 든 71종 가운데 19종이 헬스케어에서 나왔다. 같은 날 아시아에서는 정반대로 올해 가장 많이 오른 AI·반도체가 무더기로 팔려 중국A 반도체 지수가 7.7% 빠졌다. 장기금리가 19년 최고에서 물러서며 금이 4.8% 뛰었지만 그 돈이 AI 하드웨어로는 돌아가지 않았다는 것이 오늘의 요점이고, 지수가 조용한 사이 주도주 명단이 바뀌고 있다는 해석이다(추정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/19): 지수는 0.2% 오르는 데 그쳤지만 그 안에서 헬스케어와 금이라는 두 축이 동시에 터진 하루다. 신고가가 112종으로 불어난 반면 신저가는 13종에 머물렀는데, 새로 들어온 71종의 성격이 뚜렷하다. 머크가 12.6% 오르며 대형 제약 가운데 가장 크게 뛰었고 모더나는 177% 폭등했으며, 다나허와 서모피셔 같은 생명과학 장비까지 함께 신고가에 올라 헬스케어 ETF는 3.5% 상승했다. 귀금속은 더 일사불란해서 뉴몬트와 배릭을 포함한 대형 금광 11종이 하나도 빠짐없이 7에서 14% 사이로 올랐는데, 금 현물이 4,575달러까지 4.8% 뛴 결과다. 주목할 것은 기술주 안의 균열로, 어도비와 인튜이트 등 소프트웨어 13종이 신고가에 든 반면 반도체와 하드웨어 96종에서는 신고가가 한 종도 나오지 않았고 설계도구업체 케이던스는 오히려 신저가로 내려갔다. 신저가 쪽은 3분기 가이던스가 컨센서스에 못 미친 TJX와, 투자의견 강등을 함께 맞은 캐나다 파이프라인 TC에너지·엔브리지가 채웠다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/19): 올해 가장 많이 오른 업종이 가장 많이 맞은 날이었다. 철강·비철이 7.3% 빠졌는데 이 업종은 연초 이후 46% 올라 17개 업종 중 1위였고, 은행도 4.2% 밀렸지만 여전히 연간 2위 자리를 지키고 있다. 반대로 올해 유일하게 마이너스인 부동산은 0.3% 하락에 그쳐 가장 덜 빠졌으니, 이날 매도는 업종의 좋고 나쁨이 아니라 그동안 얼마나 올랐느냐를 따라 움직였다. 닛케이 연동 ETF 기준으로 3.0% 하락해 이틀 연속 큰 폭의 조정이었고, 신저가 9종에는 다이세이·가지마·오바야시 3대 건설사가 나란히 들어왔다. 신고가는 젠쇼와 혼다, 올림푸스 3종뿐이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/19): 지수는 보합인데 실적을 발표한 기술주만 골라서 무너진 하루다. 항셍은 0.09% 올랐지만 항셍테크는 1.21% 밀려 연초 대비 손실이 15%로 벌어졌다. 화훙반도체가 상반기 순이익 72% 감소를 내놓으며 11.8% 급락했고 바이두도 2분기 순이익이 68% 줄어 11.0% 떨어지면서 둘 다 신저가로 내려갔으며, AI연산 칩을 만드는 일루바타코어엑스는 13.4% 빠졌다. 반대편 신고가에는 이노벤트바이오로직스와 비원메디슨즈 같은 신약 개발사가 올라와, 미국 헬스케어 랠리와 같은 방향으로 움직였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/19): 테크에 있던 자금이 통째로 은행으로 옮겨간 날이다. 상해종합이 2.40%, CSI300이 2.90% 내리는 동안 5G 지수는 8.1%, 반도체는 7.7% 빠진 반면 은행 지수만 1.6% 올랐다. 신고가 8종 가운데 중신은행과 상하이은행, 닝보은행까지 은행이 4종을 차지했고 산둥골드가 6.5% 오르며 금값 강세를 따라갔다. 하필 반도체가 가장 크게 맞은 이유는 이 지수가 올해 42.8% 올라 13개 업종 중 1위였기 때문이며, 일본과 같은 성격의 되돌림이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①금이 4,575달러 위에서 버티는지 — 금리인상 우려 후퇴가 진짜 재료라면 금은 유지되고 광산주 신고가도 이익 재평가로 이어지지만, 하루짜리 되돌림이면 광산주가 먼저 무너진다 ②머크·모더나 3상의 상세 데이터와 학회 발표 — 지금 주가는 성공 여부에만 반응했고 효과 크기와 안전성은 아직 숫자로 확인되지 않았다 ③아시아 AI 하드웨어가 미국 소프트웨어처럼 금리 하락의 수혜로 돌아서는지 — 같은 금리 재료를 두고 미국 소프트웨어는 오르고 아시아 반도체는 빠졌으니, 이 격차가 좁혀지는지가 되돌림의 끝을 알려준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 오늘은 하나의 임상 결과가 두 회사에 전혀 다른 크기로 꽂힌 것이 교재다. 흑색종 mRNA 암백신 3상 성공이라는 똑같은 재료에 모더나는 177%, 머크는 12.6% 올랐다. 배수로는 14배 차이지만 늘어난 시가총액을 보면 모더나가 약 160억달러인 반면 머크는 약 420억달러로 오히려 머크가 더 컸는데, 이 역전이 핵심이다. 퍼센트는 새로 생긴 자산을 기존 몸집으로 나눈 값이라 시가총액 250억달러짜리 모더나에서 크게 튀는 것이고, 절대 금액은 그 자산 자체의 가치라서 공동개발 지분을 나눠 가진 두 회사가 비슷하게 반영한다. 게다가 머크에게 이 백신은 새 매출이 늘어나는 이익 경로만이 아니라, 키트루다 특허 만료 이후를 무엇으로 메울지에 대한 답이기도 해서 할인율에 얹혀 있던 절벽 위험을 걷어내는 멀티플 경로로도 작동한다. 그래서 재료를 들었을 때 순서는 이렇다 — 먼저 그 자산의 절대 가치를 추정하고, 그다음 회사별 지분과 시가총액으로 나눠보면 어느 쪽이 몇 퍼센트 움직여야 맞는지가 나온다. 이번 건은 두 회사가 공개할 분담 구조와 로열티 조건, 그리고 머크의 2028년 이후 매출 가이던스가 바뀌는지로 확인할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 08:06 KST 실행이라 미국은 8/19(수) 마감 약 3시간 후 확정치이고, 일본·홍콩·중국A도 모두 8/19 마감분이라 전 시장 정상 갱신이다. 스크립트가 만든 index CSV의 닛케이가 8/18에서 멈춰 있어 일본 지수 낙폭은 닛케이 연동 ETF(1321 JP) 종가로 계산한 3.0%를 사용했다. ETF 44/44·지수 8/8 수집 정상이고 PER은 TradingView 12개월 선행 배수이며, 중국A는 선행 PER 표본이 얇아 밸류 수치 인용을 보류했다. 회사PC 자격증명 문제로 볼트 pull이 실패해 텔레그램 적재분은 사용하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7707.98</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>2.65</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>4.82</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26331.09</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>-0.97</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>1.91</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>13.29</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6869.83</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-1.55</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-8.32</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>63.02</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>67460.73</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-2.54</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>11.41</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>34.01</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3894.42</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>-1.32</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-4.48</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-1.88</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4588.7</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>-2.9</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>-2.18</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-3.18</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-4.06</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>-0.89</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25495.07</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.09</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>1.44</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-1.17</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-0.53</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4682.05</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>-1.21</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-1.98</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>-2.76</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-3.61</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-15.12</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>31</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-1</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1803,7 @@
       <c r="F17" t="n">
         <v>-2</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2045,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2002,7 +2084,7 @@
       <c r="F24" t="n">
         <v>-2</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2041,7 +2123,7 @@
       <c r="F25" t="n">
         <v>-2</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2082,7 +2164,7 @@
       <c r="F26" t="n">
         <v>-3</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2841,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2800,7 +2882,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2839,7 +2921,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2878,7 +2960,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2917,7 +2999,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2958,7 +3040,7 @@
       <c r="F48" t="n">
         <v>-1</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2999,7 +3081,7 @@
       <c r="F49" t="n">
         <v>-1</v>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3038,7 +3120,7 @@
       <c r="F50" t="n">
         <v>-2</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3079,7 +3161,7 @@
       <c r="F51" t="n">
         <v>-2</v>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3395,7 +3477,7 @@
       <c r="F59" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3436,7 +3518,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3475,7 +3557,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3516,7 +3598,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3555,7 +3637,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3594,7 +3676,7 @@
       <c r="F64" t="n">
         <v>-1</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3635,7 +3717,7 @@
       <c r="F65" t="n">
         <v>-1</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1.1% 하락. 소프트웨어는 신고가 13종을 냈지만 반도체·하드웨어는 신고가가 전무해 내부가 갈렸다. 연간 2위(27.9%)는 유지.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>3.5% 급등으로 전 섹터 1위. 머크·모더나 암백신 3상 성공에 헬스케어 신고가만 31종이 쏟아졌고 1개월 수익률도 9.6%로 최상위.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>0.6% 하락. 장기금리가 19년 최고에서 물러선 것이 이자마진에 부담으로 읽혔다는 해석(추정). 신고가 9종은 유지.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1.9% 상승으로 헬스케어 다음. 다만 신저가에 TJX가 들어와 오프프라이스 유통은 가이던스 실망으로 따로 놀았다.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>0.8% 상승. 신고가 2종에 그쳐 존재감은 옅고 연간 수익률은 -4.9%로 11개 섹터 중 최하위다.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>0.9% 하락. 신저가 4종이 나와 순강도 -2로 약세 판정이며, 록웰오토메이션과 올드도미니언이 신저가에 들어왔다.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1.1% 상승. 금리 반락과 위험자산 회피가 겹친 방어주 매수로 보이며(추정), 신고가 6종을 냈다.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>0.2% 하락했지만 연간 44.2%로 여전히 1위. 브렌트 91.7달러 강세에도 신고가 16종은 유지돼 조정보다 숨고르기에 가깝다.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>44.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>보합. 1개월 -2.0%로 유일하게 마이너스이고 신고가 없이 신저가 1종이 나와 약세 판정이다.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1.4% 상승. 금 4.8% 급등에 힘입어 귀금속 광산 11종이 전부 신고가를 내며 소재 전체를 끌어올렸다.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>0.8% 상승. 장기금리 반락의 직접 수혜로 읽히지만(추정) 1개월은 -0.5%로 아직 회복 국면은 아니다.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>11</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-7.3</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>14</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>43.3</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-14.7</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>7.7% 폭락으로 A주 최악. 올해 42.8% 올라 13개 중 1위였던 자리가 그대로 되돌림의 크기가 됐다.</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-7.7</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>42.8</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>7.2% 급락. 연간 3위(27.6%) 자리에서 밀려났고 신고가 없이 신저가만 나와 약세 판정이다.</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>8.1% 하락으로 이날 낙폭 1위. 연간 2위(33.3%) 업종이 가장 크게 맞은 전형적인 주도주 되돌림이다.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-8.1</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-7.4</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>3.1% 하락. 3개월 -19.5%로 이미 오래 밀려온 터라 이날 낙폭은 상대적으로 작았다.</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-19.5</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>5.2% 하락. 3개월 -17.1%에 이어 연간 -19.3%로 하위권이며 반등 시도가 계속 무산되는 모습.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-19.3</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>5.1% 하락. 1개월은 3.7% 올랐지만 3개월 -22.7%로 13개 중 낙폭이 가장 커 추세 회복은 아직 멀다.</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.7</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1.8% 하락. 연간 -20.7%로 최하위이나 이날은 테크 폭락 대비 방어적이었다.</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-20.7</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1.6% 상승으로 유일한 플러스. 테크에서 빠진 자금이 저평가 고배당으로 이동해 은행 4종이 신고가를 냈다.</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>3.6% 하락. 미국 금값 급등은 중국 장 마감 이후에 나온 재료라 이날 A주 유색금속에는 반영되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>2.0% 하락. 주간 -5.0%로 낙폭이 커지며 연간 -19.4%까지 밀렸다.</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-19.4</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>1.4% 하락. 지수가 2.9% 빠진 날치고는 방어적이었으나 1개월 -5.4%로 거래대금 둔화 우려가 남는다.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>1.2% 하락에 그쳐 방어. 3개월 13.5%로 A주 1위이며 홍콩 신약주 강세와 같은 방향이다.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1.0% 하락으로 선방. 양위안음료가 신고가에 들며 소비 방어주로 자금이 일부 옮겨간 흔적이다.</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-8.1"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-5"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-8.699999999999999"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-22.7"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-20.7"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7816,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7641,10 +7869,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7693,19 +7921,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 엑손모빌(석유·가스 통합메이저): 이란 긴장으로 브렌트 90달러, 유가 강세 직접 수혜</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7753,10 +7981,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7805,10 +8033,10 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7861,10 +8089,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>머크(제약, 키트루다 보유): 모더나와 공동 흑색종 mRNA 암백신 3상 성공에 목표가 상향 잇따라</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7917,15 +8149,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7969,15 +8201,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8021,10 +8253,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8073,10 +8305,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8123,19 +8355,19 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 길리어드사이언스(HIV·간질환 치료제): HIV 부문 성장과 가이던스 상향으로 투자심리 개선</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8179,10 +8411,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8231,15 +8463,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8281,15 +8513,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8331,15 +8563,19 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>TJX컴퍼니스(TJ맥스 등 오프프라이스 유통): 2분기 호실적에도 3분기 EPS 가이던스 컨센 하회</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8383,10 +8619,10 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8435,15 +8671,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8487,15 +8723,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8543,15 +8779,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8599,15 +8835,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8651,10 +8887,10 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8703,15 +8939,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8759,15 +8995,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8811,15 +9047,19 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>엔브리지(캐나다 원유·가스 파이프라인): TD코웬 강등과 라인5 법적 리스크 부각</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8863,15 +9103,15 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8915,15 +9155,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8967,10 +9207,14 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>아그니코이글마인스(금 채굴): 달러 약세와 장기금리 반락으로 금값 급등 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9019,15 +9263,15 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9071,10 +9315,10 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9127,15 +9371,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9179,15 +9423,15 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9231,10 +9475,10 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9283,10 +9527,10 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9339,15 +9583,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>리제네론(바이오제약): 개별 뉴스 없음, 헬스케어 섹터 급등에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9395,15 +9643,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9447,10 +9695,10 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9499,15 +9747,15 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9551,10 +9799,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9607,15 +9855,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9663,10 +9911,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9711,15 +9959,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9763,10 +10011,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9815,15 +10063,15 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9867,15 +10115,19 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>TC에너지(캐나다 천연가스 파이프라인): TD코웬 투자의견 강등, 성장 스토리 소진 우려</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9919,10 +10171,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9975,19 +10227,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>(전일) 세노버스에너지(캐나다 석유·가스 통합기업): 이란·호르무즈 리스크發 유가 강세 수혜</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10031,15 +10283,15 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10083,10 +10335,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10135,15 +10387,15 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10187,10 +10439,10 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10243,15 +10495,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>벡톤디킨슨(주사기·진단 등 의료기기): 개별 뉴스 없음, 헬스케어 랠리 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10295,15 +10551,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10347,10 +10603,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10399,19 +10655,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>(전일) 레볼루션메디슨스(RAS 표적 항암신약 바이오텍): 애널리스트 목표주가 잇단 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10455,10 +10711,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10505,19 +10761,19 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업 소프트웨어): 4분기 실적 서프라이즈에 BofA 등 목표주가 대거 상향</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10561,15 +10817,15 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10613,15 +10869,15 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10665,15 +10921,15 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10715,15 +10971,19 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>에스티로더(화장품·뷰티): FY26 4분기 실적 서프라이즈와 FY27 EPS 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10771,10 +11031,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10823,15 +11083,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10875,15 +11135,15 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10927,15 +11187,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10979,15 +11239,15 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11035,15 +11295,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11091,15 +11351,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11143,10 +11403,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11195,10 +11455,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11251,15 +11511,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11307,10 +11567,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11359,15 +11619,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11411,15 +11671,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>모더나(mRNA 백신·항암치료제): 머크와 공동개발 흑색종 mRNA 암백신 3상 성공</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11463,15 +11727,19 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>커티스라이트(방산·원자력 부품): 특별한 뉴스 없음(8월 실적 이후 밸류에이션 조정 지속)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11515,10 +11783,10 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11571,15 +11839,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11623,15 +11891,19 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>코어마이닝(금·은 채굴): 금 4.8%·은 4.8% 급등에 신고가 경신</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11673,15 +11945,15 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11725,10 +11997,10 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11775,15 +12047,15 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11827,10 +12099,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11883,19 +12155,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="8" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>(전일) 퍼미안리소시스(셰일 원유 생산): 웰스파고 목표주가 상향(26→27달러)에 유가 강세 동반</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11939,15 +12211,15 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11991,15 +12263,15 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12047,10 +12319,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12099,10 +12371,10 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12155,10 +12427,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12211,15 +12483,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12263,10 +12535,10 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12315,10 +12587,10 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12371,10 +12643,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12423,15 +12695,15 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12475,15 +12747,15 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12527,10 +12799,10 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12579,10 +12851,10 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12631,15 +12903,15 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12683,10 +12955,10 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12735,15 +13007,15 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12787,15 +13059,15 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12841,15 +13113,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="8" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12893,10 +13165,10 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" s="8" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12947,15 +13219,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N102" s="8" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12999,15 +13271,19 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" s="8" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr">
+        <is>
+          <t>헤클라마이닝(은 채굴): 금리인상 우려 후퇴로 금·은값 급등, 광산주 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13055,15 +13331,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N104" s="8" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13107,10 +13383,10 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="8" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13163,10 +13439,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="8" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13219,19 +13495,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N107" s="8" t="inlineStr">
+      <c r="N107" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓츠코(냉난방공조 유통): 30년물 금리 2007년래 최고에 주택·건자재 수요 우려 확산</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13273,15 +13549,15 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" s="8" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13323,15 +13599,15 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" s="8" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13373,10 +13649,10 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13429,15 +13705,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="8" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13481,15 +13757,15 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="8" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13531,15 +13807,15 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" s="8" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13581,15 +13857,19 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr">
+        <is>
+          <t>인라이트리뉴어블(태양광·풍력 발전 개발): 특별한 뉴스 없음(밸류에이션 부담·차익실현 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13633,10 +13913,10 @@
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" s="8" t="inlineStr"/>
+      <c r="N115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13685,15 +13965,15 @@
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" s="8" t="inlineStr"/>
+      <c r="N116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13739,15 +14019,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N117" s="8" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13791,15 +14071,15 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" s="8" t="inlineStr"/>
+      <c r="N118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13843,15 +14123,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N119" s="8" t="inlineStr"/>
+      <c r="N119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13895,10 +14175,10 @@
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" s="8" t="inlineStr"/>
+      <c r="N120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13951,19 +14231,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N121" s="8" t="inlineStr">
+      <c r="N121" s="10" t="inlineStr">
         <is>
           <t>(전일) 달링인그리디언츠(동물부산물·재생연료 원료): 2분기 사상최대 실적·자사주 10억달러 여진</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14007,10 +14287,10 @@
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" s="8" t="inlineStr"/>
+      <c r="N122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14059,15 +14339,15 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" s="8" t="inlineStr"/>
+      <c r="N123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14111,15 +14391,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N124" s="8" t="inlineStr"/>
+      <c r="N124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14159,10 +14439,10 @@
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" s="8" t="inlineStr"/>
+      <c r="N125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14215,7 +14495,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N126" s="8" t="inlineStr"/>
+      <c r="N126" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N126"/>
@@ -14321,12 +14601,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14368,15 +14648,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>혼다(자동차·이륜차 제조): 개별 뉴스 없음, 신고가권에서 차익실현 매도</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14418,10 +14702,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>다이킨공업(에어컨·공조기기): 외국계 목표주가 하향과 실적 실망감에 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14468,14 +14756,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시지쇼(도심 오피스 개발·임대): 10년물 2.945% 급등에 부동산 매도, 연중 신저가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14528,19 +14816,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰이부동산(오피스·주택 개발): 금리 급등에 조달비용·자산가치 우려로 연중 신저가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14582,10 +14870,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14632,19 +14920,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 스미토모부동산(도쿄 오피스 중심 대형 디벨로퍼): 30년물 국채금리 최고치·일본은행 추가 인상 경계로 부동산주 매도</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14688,10 +14976,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>구보타(농기계·건설기계): 개별 뉴스 없음, 기계 업종 4.0% 하락에 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14744,14 +15036,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 니혼유센(벌크·컨테이너 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14800,15 +15092,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14850,10 +15142,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>가지마건설(종합건설): 금리 상승에 따른 건설 수요 둔화 우려로 건설주 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14904,19 +15200,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 올림푸스(내시경 등 의료기기): 회계연도 실적 저점 통과 기대에 매수세 지속</t>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>올림푸스(내시경 등 의료기기): 실적 회복 기대와 자사주 매입 확대로 매수세 지속</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14958,15 +15254,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>오바야시구미(종합건설): 금리 상승에 따른 건설 수요 둔화 우려로 건설주 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15008,10 +15308,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>다이세이건설(종합건설): 금리 상승에 따른 건설 수요 둔화 우려로 건설주 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15064,19 +15368,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 가와사키기선(컨테이너선 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15122,7 +15426,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>젠쇼홀딩스(규동 스키야 등 외식체인): 가격 인상 효과에 따른 실적 개선 기대 지속</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N16"/>
@@ -15228,12 +15536,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15277,15 +15585,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>비원메디슨즈(항암 신약 개발): 상반기 순이익 386% 급증 등 실적 호조</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15329,10 +15641,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>화훙반도체(성숙공정 파운드리): 상반기 순이익 72% 급감 실적 쇼크</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15385,19 +15701,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운홀딩스(컨테이너 해운): 특별한 뉴스 없음(호르무즈발 운임 강세 지속 추정)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15439,10 +15755,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>바이두(AI 검색·클라우드): 2분기 순이익 68% 급감, 광고 부진에 1년 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15495,19 +15815,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시바이오로직스(바이오의약품 위탁개발생산): 신약목록 편입 기대에 업종 상승률 선두</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15553,10 +15873,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>차이나유니콤(중국 3대 통신사): 개별 뉴스 미확인, 수급 이탈로 급락 추정</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15607,19 +15931,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 콰이쇼우(중국 2위 숏폼동영상·라이브커머스): 전자상거래 거래액 성장 둔화 우려, 8/20 실적발표 앞두고 신저가</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15663,15 +15987,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>이노벤트바이오로직스(항체 신약 개발): 개별 뉴스 없음, 신약 섹터 강세에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15715,15 +16043,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15765,10 +16093,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>스와이어프로퍼티스(홍콩 상업용 부동산): 씨티의 홍콩 소매경기 하반기 개선 전망 보고서</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15819,19 +16151,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15879,15 +16211,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>화넝파워인터내셔널(석탄화력 발전): 개별 뉴스 미확인, 섹터 수급 이탈 추정</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15927,10 +16263,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>일루바타코어엑스(AI연산용 GPU 반도체): 해외 반도체주 급락 전이로 동반 급락 추정</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15981,14 +16321,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 싸이리스그룹(신에너지차 완성차): 원제 브랜드 판매 급감 여진, 실적 부진 우려 지속</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16041,10 +16381,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16095,14 +16435,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국남방항공(항공운송): 중동 긴장발 유가 급등으로 항공유 비용 부담 확대</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16149,10 +16489,10 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16203,14 +16543,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국철도건설(철도·인프라 시공): 특별한 뉴스 없음(수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16259,19 +16599,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국동방항공(항공운송): 중동 긴장발 유가 급등으로 항공유 비용 부담 확대</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16315,7 +16655,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N21"/>
@@ -16421,12 +16761,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16466,10 +16806,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>중신은행(전국구 주식제 상업은행): 테크주 급락 자금이 저평가 고배당 은행으로 이동</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16518,19 +16862,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16572,10 +16916,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>닝보은행(도시상업은행): 주력자금 순유입 지속, 저평가 고배당 방어주 로테이션 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16624,19 +16972,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 화뎬신에너지(화뎬그룹 산하 신재생 발전사): 특별한 뉴스 없음(신재생 발전주 약세 흐름 속 신저가)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16680,15 +17028,19 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>상하이은행(도시상업은행): 은행·배당 ETF 자금 유입 지속, 방어주 로테이션에 사상 최고가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16730,15 +17082,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>산둥골드(중국 최대 금광기업): 국제 금값 급등과 안전자산 수요로 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16780,15 +17136,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16832,15 +17188,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>선전자리촹(PCB 제조, 8월 4일 신규 상장): 상장 초기 단타자금 이탈로 하한가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16882,10 +17242,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16936,19 +17296,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 싸이리스그룹(신에너지차 완성차): 원제 7월 판매 전년비 51% 급감 여진으로 신저가</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16994,15 +17354,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>중국동방항공(항공 운송): 국제유가 상승에 따른 항공유 비용 부담과 시장 약세 동반</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17048,7 +17412,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>양위안음료(호두음료 제조): 특별한 뉴스 없음(테크 급락 속 소비 방어주 수급 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
